--- a/docs/data_quality_issue_log.xlsx
+++ b/docs/data_quality_issue_log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6e62e7c97e835051/Altieri/Estudos/Sistemas/Plano Carreira/Bases Hashtag - Treinamentos/11. Aula Claude/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="163" documentId="11_45BF4D4A499C6BE22BBCFB55AE45EE75FAB251AA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D3EDAD8-3229-4A30-AC1A-9E6C56D9158B}"/>
+  <xr:revisionPtr revIDLastSave="184" documentId="11_45BF4D4A499C6BE22BBCFB55AE45EE75FAB251AA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F12B7C6F-E600-43B2-962A-09F7996FBC7C}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="6108" yWindow="4068" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Issue Log" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="75">
   <si>
     <t>Data Quality Issue Log — Investments BI Project</t>
   </si>
@@ -259,6 +259,38 @@
   </si>
   <si>
     <t>out of format email</t>
+  </si>
+  <si>
+    <t>dim_account</t>
+  </si>
+  <si>
+    <t>client_id</t>
+  </si>
+  <si>
+    <t>SELECT da.client_id, dc.client_id 
+FROM dim_account da 
+LEFT JOIN dim_client dc
+ON da.client_id = dc.client_id 
+WHERE dc.client_id IS NULL</t>
+  </si>
+  <si>
+    <t>investigate the correct client and relink, otherwise isolate or remove the orphan</t>
+  </si>
+  <si>
+    <t>orphan FK</t>
+  </si>
+  <si>
+    <t>advisor_id</t>
+  </si>
+  <si>
+    <t>SELECT dacc.advisor_id 
+FROM dim_account dacc
+LEFT JOIN dim_advisor daa
+ON daa.advisor_id = dacc.advisor_id 
+WHERE daa.advisor_id IS NULL</t>
+  </si>
+  <si>
+    <t>relink to a valid advisor, or isolate/remove the orphan account</t>
   </si>
 </sst>
 </file>
@@ -704,7 +736,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="5" customWidth="1"/>
@@ -715,7 +747,7 @@
     <col min="7" max="7" width="18" style="6" customWidth="1"/>
     <col min="8" max="8" width="13.6640625" style="5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="21.77734375" style="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.88671875" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.88671875" style="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10" style="5" customWidth="1"/>
     <col min="12" max="16384" width="8.88671875" style="5"/>
   </cols>
@@ -976,6 +1008,61 @@
       </c>
       <c r="K12" s="5" t="s">
         <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="5">
+        <v>9</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F13" s="5">
+        <v>1</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
+        <v>10</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="F14" s="5">
+        <v>1</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data_quality_issue_log.xlsx
+++ b/docs/data_quality_issue_log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6e62e7c97e835051/Altieri/Estudos/Sistemas/Plano Carreira/Bases Hashtag - Treinamentos/11. Aula Claude/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="184" documentId="11_45BF4D4A499C6BE22BBCFB55AE45EE75FAB251AA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F12B7C6F-E600-43B2-962A-09F7996FBC7C}"/>
+  <xr:revisionPtr revIDLastSave="236" documentId="11_45BF4D4A499C6BE22BBCFB55AE45EE75FAB251AA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A6DE931-E869-4BD8-B879-1F884327890E}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="6108" yWindow="4068" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Issue Log" sheetId="1" r:id="rId1"/>
@@ -19,12 +19,25 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Issue Log'!$A$4:$K$4</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
   <si>
     <t>Data Quality Issue Log — Investments BI Project</t>
   </si>
@@ -291,6 +304,71 @@
   </si>
   <si>
     <t>relink to a valid advisor, or isolate/remove the orphan account</t>
+  </si>
+  <si>
+    <t>account_type</t>
+  </si>
+  <si>
+    <t>SELECT account_type, COUNT(*)
+FROM dim_account da 
+GROUP BY account_type</t>
+  </si>
+  <si>
+    <t>standardize case</t>
+  </si>
+  <si>
+    <t>base_currency</t>
+  </si>
+  <si>
+    <t>SELECT base_currency , COUNT(*)
+FROM dim_account
+WHERE base_currency  NOT IN ('USD','BRL','EUR') 
+GROUP BY base_currency</t>
+  </si>
+  <si>
+    <t>5 - pct=8.3%</t>
+  </si>
+  <si>
+    <t>open_date</t>
+  </si>
+  <si>
+    <t>date format</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) as rows_affected,
+	ROUND(100.0 * COUNT (*) / (SELECT COUNT(*) FROM dim_account) ,1) as pct 
+FROM dim_account da 
+WHERE DATE(da.open_date) IS NULL</t>
+  </si>
+  <si>
+    <t>null</t>
+  </si>
+  <si>
+    <t>SELECT open_date 
+FROM dim_account da
+WHERE da.open_date IS NULL 
+OR TRIM(da.open_date ) = ''</t>
+  </si>
+  <si>
+    <t>using power query - power bi</t>
+  </si>
+  <si>
+    <t>dim_advisor</t>
+  </si>
+  <si>
+    <t>Low/cosmetic</t>
+  </si>
+  <si>
+    <t>advisor_name</t>
+  </si>
+  <si>
+    <t>upper/lower case</t>
+  </si>
+  <si>
+    <t>SELECT advisor_name 
+FROM dim_advisor
+WHERE advisor_name IS NULL
+OR TRIM(advisor_name ) = ''</t>
   </si>
 </sst>
 </file>
@@ -736,7 +814,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="5" customWidth="1"/>
@@ -1064,6 +1142,151 @@
       <c r="J14" s="12" t="s">
         <v>74</v>
       </c>
+      <c r="K14" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="5">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="F15" s="5">
+        <v>10</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J15" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
+        <v>12</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J16" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="144" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
+        <v>13</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F17" s="5">
+        <v>34</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J17" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
+        <v>13</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="F18" s="5">
+        <v>4</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
+        <v>14</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:K4" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/docs/data_quality_issue_log.xlsx
+++ b/docs/data_quality_issue_log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6e62e7c97e835051/Altieri/Estudos/Sistemas/Plano Carreira/Bases Hashtag - Treinamentos/11. Aula Claude/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="236" documentId="11_45BF4D4A499C6BE22BBCFB55AE45EE75FAB251AA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A6DE931-E869-4BD8-B879-1F884327890E}"/>
+  <xr:revisionPtr revIDLastSave="280" documentId="11_45BF4D4A499C6BE22BBCFB55AE45EE75FAB251AA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A141A58-2AEE-40A0-A04A-ADBCC1F05300}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="102">
   <si>
     <t>Data Quality Issue Log — Investments BI Project</t>
   </si>
@@ -369,6 +369,45 @@
 FROM dim_advisor
 WHERE advisor_name IS NULL
 OR TRIM(advisor_name ) = ''</t>
+  </si>
+  <si>
+    <t>SELECT COUNT (*) as rows_affected,
+	ROUND(100.0 * COUNT(*) / (SELECT COUNT(*) FROM dim_advisor),1 ) as pct
+FROM dim_advisor
+WHERE DATE (hire_date ) IS NULL</t>
+  </si>
+  <si>
+    <t>7 / pct=77.8%</t>
+  </si>
+  <si>
+    <t>hire_date</t>
+  </si>
+  <si>
+    <t>SELECT advisor_name, COUNT(*)
+FROM dim_advisor
+GROUP BY advisor_name 
+HAVING COUNT(*) &gt; 1</t>
+  </si>
+  <si>
+    <t>advisor duplicated/same name id duplicated</t>
+  </si>
+  <si>
+    <t>consolitade into a single advisor</t>
+  </si>
+  <si>
+    <t>dim_currency</t>
+  </si>
+  <si>
+    <t>currency_name</t>
+  </si>
+  <si>
+    <t>SELECT dc.currency_name
+FROM dim_currency dc
+WHERE currency_name IS NULL
+OR TRIM(currency_name ) = ''</t>
+  </si>
+  <si>
+    <t>missing name = Euro</t>
   </si>
 </sst>
 </file>
@@ -388,27 +427,32 @@
       <sz val="14"/>
       <color rgb="FF1F3864"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF595959"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -814,7 +858,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="5" customWidth="1"/>
@@ -1278,6 +1322,9 @@
       <c r="E19" s="12" t="s">
         <v>91</v>
       </c>
+      <c r="F19" s="5">
+        <v>1</v>
+      </c>
       <c r="H19" s="5" t="s">
         <v>88</v>
       </c>
@@ -1285,6 +1332,93 @@
         <v>86</v>
       </c>
       <c r="K19" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
+        <v>15</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="F20" s="5">
+        <v>2</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J20" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="5">
+        <v>16</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J21" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A22" s="5">
+        <v>17</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D22" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="F22" s="5">
+        <v>1</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J22" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="K22" s="5" t="s">
         <v>16</v>
       </c>
     </row>

--- a/docs/data_quality_issue_log.xlsx
+++ b/docs/data_quality_issue_log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6e62e7c97e835051/Altieri/Estudos/Sistemas/Plano Carreira/Bases Hashtag - Treinamentos/11. Aula Claude/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="280" documentId="11_45BF4D4A499C6BE22BBCFB55AE45EE75FAB251AA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A141A58-2AEE-40A0-A04A-ADBCC1F05300}"/>
+  <xr:revisionPtr revIDLastSave="411" documentId="11_45BF4D4A499C6BE22BBCFB55AE45EE75FAB251AA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3B985C54-FC45-4418-9A0C-88C0AC9F2C2F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-14505" yWindow="-2385" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Issue Log" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="143">
   <si>
     <t>Data Quality Issue Log — Investments BI Project</t>
   </si>
@@ -408,6 +408,167 @@
   </si>
   <si>
     <t>missing name = Euro</t>
+  </si>
+  <si>
+    <t>dim_security</t>
+  </si>
+  <si>
+    <t>security_id</t>
+  </si>
+  <si>
+    <t>duplicates</t>
+  </si>
+  <si>
+    <t>SELECT ticker, count(*)
+FROM dim_security
+GROUP BY ticker
+HAVING COUNT(*) &gt; 1</t>
+  </si>
+  <si>
+    <t>keep one security_id</t>
+  </si>
+  <si>
+    <t>asset_class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SELECT asset_class, COUNT(*) 
+FROM dim_security
+GROUP BY asset_class </t>
+  </si>
+  <si>
+    <t>sector</t>
+  </si>
+  <si>
+    <t>SELECT ds.sector, ds.security_id  , ds.ticker 
+FROM dim_security ds 
+WHERE ds.sector IS NULL
+OR TRIM(ds.sector ) = ''</t>
+  </si>
+  <si>
+    <t>isin</t>
+  </si>
+  <si>
+    <t>SELECT isin
+FROM dim_security
+WHERE isin IS NULL 
+OR TRIM(isin) = ''</t>
+  </si>
+  <si>
+    <t>fact_fx_rate</t>
+  </si>
+  <si>
+    <t>rade_date</t>
+  </si>
+  <si>
+    <t>SELECT rate_date
+FROM fact_fx_rate
+WHERE DATE(rate_date ) IS NULL</t>
+  </si>
+  <si>
+    <t>84 / 5.4%</t>
+  </si>
+  <si>
+    <t>rate_to_usd</t>
+  </si>
+  <si>
+    <t>SELECT ffr.rate_to_usd
+FROM fact_fx_rate ffr
+WHERE ffr.rate_to_usd  IS NULL OR TRIM(ffr.rate_to_usd ) = ''</t>
+  </si>
+  <si>
+    <t>negative/zero values</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+SELECT ffr.rate_to_usd
+FROM fact_fx_rate ffr
+WHERE TRIM(ffr.rate_to_usd ) &lt;&gt; ''
+AND CAST(rate_to_usd AS REAL) &lt;= 0</t>
+  </si>
+  <si>
+    <t>fact_transaction</t>
+  </si>
+  <si>
+    <t>account_id</t>
+  </si>
+  <si>
+    <t>SELECT ft.account_id , ft.transaction_id 
+FROM fact_transaction ft
+LEFT JOIN dim_account da
+ON ft.account_id = da.account_id 
+WHERE da.account_id IS NULL</t>
+  </si>
+  <si>
+    <t>escalate to data owner; relink to valid account where possible, else map to ‘Unknown account’ bucket. Do not delete records</t>
+  </si>
+  <si>
+    <t>SELECT ft.security_id, ft.transaction_id 
+FROM fact_transaction ft
+LEFT JOIN dim_security ds 
+ON ft.security_id = ds.security_id
+WHERE ds.security_id IS NULL AND TRIM(ft.security_id) &lt;&gt; ''</t>
+  </si>
+  <si>
+    <t>escalate to data owner; relink 5000 to the correct security if identifiable, else map to “Unknown security”; do not delete</t>
+  </si>
+  <si>
+    <t>SELECT COUNT(*) AS qtt,
+	ROUND(100.0 * COUNT(*) / (SELECT COUNT(*) FROM fact_transaction), 1)
+FROM fact_transaction
+WHERE DATE(transaction_date ) IS NULL</t>
+  </si>
+  <si>
+    <t>transactio_date</t>
+  </si>
+  <si>
+    <t>3348 / 55.6%</t>
+  </si>
+  <si>
+    <t>transactio_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SELECT transaction_type, COUNT(*)
+FROM fact_transaction
+GROUP BY transaction_type </t>
+  </si>
+  <si>
+    <t>pattern TRIM</t>
+  </si>
+  <si>
+    <t>quantity</t>
+  </si>
+  <si>
+    <t>negative values</t>
+  </si>
+  <si>
+    <t>SELECT quantity 
+FROM fact_transaction
+WHERE CAST(quantity AS REAL) &lt; 0 AND TRIM(quantity ) &lt;&gt;''</t>
+  </si>
+  <si>
+    <t>escalate to data owner</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>SELECT ft.price
+FROM fact_transaction ft 
+WHERE CAST(price AS REAL) &lt; 0 AND TRIM(price) &lt;&gt;''</t>
+  </si>
+  <si>
+    <t>text in numeric</t>
+  </si>
+  <si>
+    <t>SELECT ft.price
+FROM fact_transaction ft 
+WHERE TRIM(price) &lt;&gt;'' AND price GLOB '*[^0-9.-]*'</t>
+  </si>
+  <si>
+    <t>escalate to data owner; fix sign/value at source; do not delete</t>
+  </si>
+  <si>
+    <t>convert to number in cleaning; where the real price is missing, recover from source or isolate — do not assume 0</t>
   </si>
 </sst>
 </file>
@@ -522,16 +683,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -551,6 +706,12 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -858,567 +1019,937 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9" style="5" customWidth="1"/>
-    <col min="2" max="3" width="15" style="5" customWidth="1"/>
-    <col min="4" max="4" width="26" style="12" customWidth="1"/>
-    <col min="5" max="5" width="21.44140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13" style="5" customWidth="1"/>
-    <col min="7" max="7" width="18" style="6" customWidth="1"/>
-    <col min="8" max="8" width="13.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.77734375" style="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.88671875" style="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10" style="5" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="5"/>
+    <col min="1" max="1" width="9" style="4" customWidth="1"/>
+    <col min="2" max="3" width="15" style="4" customWidth="1"/>
+    <col min="4" max="4" width="26" style="10" customWidth="1"/>
+    <col min="5" max="5" width="21.44140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" style="4" customWidth="1"/>
+    <col min="7" max="7" width="18" style="5" customWidth="1"/>
+    <col min="8" max="8" width="13.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.77734375" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.88671875" style="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10" style="4" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="5"/>
+      <c r="D1" s="4"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="5"/>
+      <c r="D2" s="4"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D3" s="5"/>
+      <c r="D3" s="4"/>
     </row>
     <row r="4" spans="1:11" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="8" t="s">
+      <c r="I4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="8" t="s">
+      <c r="J4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="145.19999999999999" x14ac:dyDescent="0.3">
-      <c r="A5" s="5">
+      <c r="A5" s="4">
         <v>1</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="K5" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="171.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="5">
+      <c r="A6" s="4">
         <v>2</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="4">
         <v>7</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="K6" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="5">
+      <c r="A7" s="4">
         <v>3</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="4">
         <v>2</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="K7" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="5">
+      <c r="A8" s="4">
         <v>4</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="4">
         <v>2</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="K8" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="144" x14ac:dyDescent="0.3">
-      <c r="A9" s="5">
+      <c r="A9" s="4">
         <v>5</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="4">
         <v>5</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="H9" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="K9" s="5" t="s">
+      <c r="K9" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="5">
+      <c r="A10" s="4">
         <v>6</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="4">
         <v>2</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="H10" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="K10" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="216" x14ac:dyDescent="0.3">
-      <c r="A11" s="5">
+      <c r="A11" s="4">
         <v>7</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="4">
         <v>4</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="K11" s="5" t="s">
+      <c r="K11" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="72" x14ac:dyDescent="0.3">
-      <c r="A12" s="5">
+      <c r="A12" s="4">
         <v>8</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="4">
         <v>20</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="K12" s="5" t="s">
+      <c r="K12" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A13" s="5">
+      <c r="A13" s="4">
         <v>9</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="4">
         <v>1</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="H13" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J13" s="12" t="s">
+      <c r="J13" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="K13" s="5" t="s">
+      <c r="K13" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="5">
+      <c r="A14" s="4">
         <v>10</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="4">
         <v>1</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H14" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J14" s="12" t="s">
+      <c r="J14" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="K14" s="5" t="s">
+      <c r="K14" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="5">
+      <c r="A15" s="4">
         <v>11</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="4">
         <v>10</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="H15" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="J15" s="12" t="s">
+      <c r="J15" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="K15" s="5" t="s">
+      <c r="K15" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="5">
+      <c r="A16" s="4">
         <v>12</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="H16" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="J16" s="12" t="s">
+      <c r="J16" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="K16" s="5" t="s">
+      <c r="K16" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="144" x14ac:dyDescent="0.3">
-      <c r="A17" s="5">
+      <c r="A17" s="4">
         <v>13</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="E17" s="12" t="s">
+      <c r="E17" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17" s="4">
         <v>34</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="H17" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J17" s="12" t="s">
+      <c r="J17" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="K17" s="5" t="s">
+      <c r="K17" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="5">
+      <c r="A18" s="4">
         <v>13</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E18" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="4">
         <v>4</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="H18" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="J18" s="12" t="s">
+      <c r="J18" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="K18" s="5" t="s">
+      <c r="K18" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="5">
+      <c r="A19" s="4">
         <v>14</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="E19" s="12" t="s">
+      <c r="E19" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19" s="4">
         <v>1</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="H19" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="J19" s="12" t="s">
+      <c r="J19" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="K19" s="5" t="s">
+      <c r="K19" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="5">
+      <c r="A20" s="4">
         <v>15</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E20" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F20" s="4">
         <v>2</v>
       </c>
-      <c r="H20" s="5" t="s">
+      <c r="H20" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J20" s="12" t="s">
+      <c r="J20" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="K20" s="5" t="s">
+      <c r="K20" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="5">
-        <v>16</v>
-      </c>
-      <c r="B21" s="5" t="s">
+      <c r="A21" s="4">
+        <v>16</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="E21" s="12" t="s">
+      <c r="E21" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F21" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="H21" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J21" s="12" t="s">
+      <c r="J21" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="K21" s="5" t="s">
+      <c r="K21" s="4" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A22" s="5">
+      <c r="A22" s="4">
         <v>17</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="E22" s="12" t="s">
+      <c r="E22" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="F22" s="5">
+      <c r="F22" s="4">
         <v>1</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="H22" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="J22" s="12" t="s">
+      <c r="J22" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="K22" s="5" t="s">
+      <c r="K22" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="4">
+        <v>18</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="F23" s="4">
+        <v>2</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="4">
+        <v>19</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="J24" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="4">
+        <v>20</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="F25" s="4">
+        <v>2</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="4">
+        <v>21</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="F26" s="4">
+        <v>4</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="4">
+        <v>22</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J27" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A28" s="4">
+        <v>23</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A29" s="4">
+        <v>24</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="144" x14ac:dyDescent="0.3">
+      <c r="A30" s="4">
+        <v>25</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="F30" s="4">
+        <v>12</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J30" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A31" s="4">
+        <v>26</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="F31" s="4">
+        <v>10</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J31" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="144" x14ac:dyDescent="0.3">
+      <c r="A32" s="4">
+        <v>27</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J32" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A33" s="4">
+        <v>28</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J33" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="K33" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="72" x14ac:dyDescent="0.3">
+      <c r="A34" s="4">
+        <v>29</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J34" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A35" s="4">
+        <v>30</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J35" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="K35" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A36" s="4">
+        <v>31</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>139</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J36" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="K36" s="4" t="s">
         <v>16</v>
       </c>
     </row>
